--- a/data/trans_camb/P1804_2016_2023-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1804_2016_2023-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-2,58</t>
+          <t>-3,12</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-3,37</t>
+          <t>-3,3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-3,17</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -0,0</t>
+          <t>-5,69; -0,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,89</t>
+          <t>-6,18; -0,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -1,17</t>
+          <t>-4,87; -1,15</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-35,89%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-28,73%</t>
+          <t>-28,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-28,52%</t>
+          <t>-30,43%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 0,46</t>
+          <t>-57,17; -3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,91; -8,86</t>
+          <t>-44,9; -6,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,81; -12,42</t>
+          <t>-42,45; -12,79</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,52</t>
+          <t>-0,4</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,7</t>
+          <t>-1,36; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; -0,38</t>
+          <t>-2,64; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,37</t>
+          <t>-1,5; 0,74</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-16,98%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-26,26%</t>
+          <t>-10,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-22,43%</t>
+          <t>-5,86%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 13,64</t>
+          <t>-23,21; 35,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,39; -5,2</t>
+          <t>-28,61; 9,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,24; -5,94</t>
+          <t>-20,18; 12,08</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,82</t>
+          <t>-1,16; 5,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 2,62</t>
+          <t>-4,36; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,96</t>
+          <t>-1,73; 3,38</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-6,98%</t>
+          <t>-3,76%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 108,57</t>
+          <t>-16,23; 105,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 25,51</t>
+          <t>-28,86; 32,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 36,37</t>
+          <t>-15,82; 40,37</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,5</t>
+          <t>-1,32; 1,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,66</t>
+          <t>-2,75; -0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; -0,49</t>
+          <t>-1,66; 0,21</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-12,62%</t>
+          <t>-1,87%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-23,65%</t>
+          <t>-14,0%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,4%</t>
+          <t>-9,32%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 8,94</t>
+          <t>-19,23; 21,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,15; -7,79</t>
+          <t>-25,64; -0,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,37; -6,62</t>
+          <t>-19,08; 2,88</t>
         </is>
       </c>
     </row>
